--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92533939974</v>
+        <v>46157.93106483589</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93106483589</v>
+        <v>46157.9336327905</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9336327905</v>
+        <v>46157.93663168335</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93663168335</v>
+        <v>46158.28189911429</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28189911429</v>
+        <v>46158.2970375142</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2970375142</v>
+        <v>46158.29784486486</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29784486486</v>
+        <v>46158.3335133847</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3335133847</v>
+        <v>46158.37207742873</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37207742873</v>
+        <v>46158.37421009056</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
